--- a/data/trans_orig/P16A10-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P16A10-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicamentos para el corazón en las dos últimas semanas en 2007</t>
+          <t>Población que ha consumido medicamentos para el corazón en las dos últimas semanas en 2007 (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4262</t>
+          <t>4164</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5627</t>
+          <t>4459</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5362</t>
+          <t>6422</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,67%</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>489802</t>
+          <t>489900</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>461862</t>
+          <t>463030</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>956191</t>
+          <t>955131</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5077</t>
+          <t>4229</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6203</t>
+          <t>6039</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>864</t>
+          <t>869</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7764</t>
+          <t>8255</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,61%</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>730412</t>
+          <t>731260</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,42%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>619291</t>
+          <t>619455</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1353218</t>
+          <t>1352727</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1360118</t>
+          <t>1360113</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,39%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1825</t>
+          <t>1814</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10033</t>
+          <t>11015</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3116</t>
+          <t>3371</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16059</t>
+          <t>16202</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6777</t>
+          <t>6410</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>22082</t>
+          <t>21182</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,6%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>627616</t>
+          <t>626634</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>635824</t>
+          <t>635835</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,72%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>673685</t>
+          <t>673542</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>686628</t>
+          <t>686373</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,51%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1305312</t>
+          <t>1306212</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1320617</t>
+          <t>1320984</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,52%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7020</t>
+          <t>7352</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>23798</t>
+          <t>22980</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10706</t>
+          <t>10295</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>27596</t>
+          <t>26581</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>20371</t>
+          <t>20926</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>43884</t>
+          <t>42851</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,14%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>495349</t>
+          <t>496167</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>512127</t>
+          <t>511795</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>95,57%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>488046</t>
+          <t>489061</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>504936</t>
+          <t>505347</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>94,84%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>990905</t>
+          <t>991938</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1014418</t>
+          <t>1013863</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>97,98%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>31472</t>
+          <t>32053</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>56433</t>
+          <t>57520</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>16899</t>
+          <t>16451</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>37076</t>
+          <t>35655</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>53480</t>
+          <t>54659</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>83741</t>
+          <t>85699</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,84%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>330277</t>
+          <t>329190</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>355238</t>
+          <t>354657</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>85,41%</t>
+          <t>85,13%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>91,86%</t>
+          <t>91,71%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>366910</t>
+          <t>368331</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>387087</t>
+          <t>387535</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,82%</t>
+          <t>91,17%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>706955</t>
+          <t>704997</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>737216</t>
+          <t>736037</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,41%</t>
+          <t>89,16%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,24%</t>
+          <t>93,09%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>39927</t>
+          <t>39910</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>64769</t>
+          <t>64559</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>22,07%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>40408</t>
+          <t>39922</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>65597</t>
+          <t>65988</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>86906</t>
+          <t>85907</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>122422</t>
+          <t>120939</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>19,03%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>227814</t>
+          <t>228024</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>252656</t>
+          <t>252673</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>77,86%</t>
+          <t>77,93%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>86,35%</t>
+          <t>86,36%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>277337</t>
+          <t>276946</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>302526</t>
+          <t>303012</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>80,87%</t>
+          <t>80,76%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>88,22%</t>
+          <t>88,36%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>513095</t>
+          <t>514578</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>548611</t>
+          <t>549610</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>80,74%</t>
+          <t>80,97%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>86,33%</t>
+          <t>86,48%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>50526</t>
+          <t>50464</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>76774</t>
+          <t>77723</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>24,04%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>36,58%</t>
+          <t>37,03%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>59299</t>
+          <t>59415</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>90046</t>
+          <t>91705</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>27,46%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>119523</t>
+          <t>121059</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>160169</t>
+          <t>159335</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>22,26%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>29,3%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>133109</t>
+          <t>132160</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>159357</t>
+          <t>159419</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>63,42%</t>
+          <t>62,97%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>75,93%</t>
+          <t>75,96%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>243862</t>
+          <t>242203</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>274609</t>
+          <t>274493</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>73,03%</t>
+          <t>72,54%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>82,24%</t>
+          <t>82,21%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>383622</t>
+          <t>384456</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>424268</t>
+          <t>422732</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>70,55%</t>
+          <t>70,7%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>78,02%</t>
+          <t>77,74%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>151478</t>
+          <t>153538</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>205422</t>
+          <t>202598</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>154492</t>
+          <t>154493</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>204222</t>
+          <t>207824</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3189,7 +3189,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>319374</t>
+          <t>322063</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>391562</t>
+          <t>393925</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,92%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3070103</t>
+          <t>3072927</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3124047</t>
+          <t>3121987</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>93,73%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3174975</t>
+          <t>3171373</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3224705</t>
+          <t>3224704</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>93,96%</t>
+          <t>93,85%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6263160</t>
+          <t>6260797</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6335348</t>
+          <t>6332659</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>94,08%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,16%</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicamentos para el corazón en las dos últimas semanas en 2012</t>
+          <t>Población que ha consumido medicamentos para el corazón en las dos últimas semanas en 2012 (tasa de respuesta: 99,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5384</t>
+          <t>4829</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3732,7 +3732,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4942</t>
+          <t>5660</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3767,7 +3767,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3787,7 +3787,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6960</t>
+          <t>6833</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3802,7 +3802,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,77%</t>
         </is>
       </c>
     </row>
@@ -3825,7 +3825,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>447721</t>
+          <t>448276</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>424397</t>
+          <t>423679</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -3875,7 +3875,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -3895,7 +3895,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>875485</t>
+          <t>875612</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1032</t>
+          <t>1030</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11406</t>
+          <t>11374</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4095,7 +4095,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5044</t>
+          <t>4344</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4110,7 +4110,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1041</t>
+          <t>1870</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>12745</t>
+          <t>13573</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,05%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>674832</t>
+          <t>674864</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>685206</t>
+          <t>685208</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4203,7 +4203,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>604170</t>
+          <t>604870</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -4218,7 +4218,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1282706</t>
+          <t>1281878</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1294410</t>
+          <t>1293581</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,92%</t>
+          <t>99,86%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1892</t>
+          <t>1927</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10576</t>
+          <t>11078</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4418,7 +4418,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4842</t>
+          <t>4939</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18492</t>
+          <t>18959</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8189</t>
+          <t>8893</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>24396</t>
+          <t>25694</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,85%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>669478</t>
+          <t>668976</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>678162</t>
+          <t>678127</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,7 +4526,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>690340</t>
+          <t>689873</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>703990</t>
+          <t>703893</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1364490</t>
+          <t>1363192</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1380697</t>
+          <t>1379993</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,36%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7116</t>
+          <t>6611</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>24033</t>
+          <t>23018</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3283</t>
+          <t>3230</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15266</t>
+          <t>15161</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4796,7 +4796,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>12917</t>
+          <t>13499</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>33168</t>
+          <t>33311</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,71%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>590584</t>
+          <t>591599</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>607501</t>
+          <t>608006</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>598806</t>
+          <t>598911</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>610789</t>
+          <t>610842</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,7 +4904,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1195521</t>
+          <t>1195378</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1215772</t>
+          <t>1215190</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,9%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>25941</t>
+          <t>26395</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>47576</t>
+          <t>47464</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,47 +5099,47 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
+          <t>6,16%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>11,08%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>27061</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>18351</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>37433</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
           <t>6,06%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>11,11%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>27061</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>18711</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>38952</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>6,06%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>49680</t>
+          <t>48209</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>79101</t>
+          <t>79476</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>9,08%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>380768</t>
+          <t>380880</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>402403</t>
+          <t>401949</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,47 +5212,47 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>88,89%</t>
+          <t>88,92%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
+          <t>93,84%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>379</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>419715</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>409343</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>428425</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
           <t>93,94%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>379</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>419715</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>407824</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>428065</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>93,94%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,28%</t>
+          <t>91,62%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>796018</t>
+          <t>795643</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>825439</t>
+          <t>826910</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,96%</t>
+          <t>90,92%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>94,49%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>34501</t>
+          <t>35322</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>60521</t>
+          <t>61236</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>26941</t>
+          <t>27108</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>50309</t>
+          <t>50540</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>67508</t>
+          <t>68688</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>101795</t>
+          <t>102590</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>15,53%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>247274</t>
+          <t>246559</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>273294</t>
+          <t>272473</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>80,34%</t>
+          <t>80,11%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>88,79%</t>
+          <t>88,52%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>302692</t>
+          <t>302461</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>326060</t>
+          <t>325893</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>85,75%</t>
+          <t>85,68%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>92,32%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>559001</t>
+          <t>558206</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>593288</t>
+          <t>592108</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>84,6%</t>
+          <t>84,47%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>89,78%</t>
+          <t>89,61%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>60718</t>
+          <t>59491</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>91342</t>
+          <t>91696</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>23,81%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>36,56%</t>
+          <t>36,7%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>70780</t>
+          <t>71001</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>104654</t>
+          <t>104574</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>26,96%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>139963</t>
+          <t>139697</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>185770</t>
+          <t>184936</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>21,9%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>29,13%</t>
+          <t>29,0%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>158509</t>
+          <t>158155</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>189133</t>
+          <t>190360</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>63,44%</t>
+          <t>63,3%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>75,7%</t>
+          <t>76,19%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>283282</t>
+          <t>283362</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>317156</t>
+          <t>316935</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>73,02%</t>
+          <t>73,04%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>81,75%</t>
+          <t>81,7%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>452017</t>
+          <t>452851</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>497824</t>
+          <t>498090</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>70,87%</t>
+          <t>71,0%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>78,05%</t>
+          <t>78,1%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>153180</t>
+          <t>155255</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>207758</t>
+          <t>211198</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,82 +6128,82 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
+          <t>4,54%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>6,18%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>159</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>170460</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>146419</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>199323</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>4,8%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>4,13%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>5,62%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>325</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>350949</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>312413</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>388024</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>5,04%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
           <t>4,48%</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>6,07%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>159</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>170460</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>144719</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>196865</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>4,8%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>4,08%</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>5,55%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>325</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>350949</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>314112</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>386473</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>5,04%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>4,51%</t>
-        </is>
-      </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,57%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3212245</t>
+          <t>3208805</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3266823</t>
+          <t>3264748</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,82 +6241,82 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>93,82%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
+          <t>95,46%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>3130</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>3378710</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>3349847</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>3402751</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>95,2%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>94,38%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>95,87%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>6167</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>6618224</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>6581149</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>6656760</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>94,96%</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>94,43%</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
           <t>95,52%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>3130</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>3378710</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>3352305</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>3404451</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>95,2%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>94,45%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>95,92%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>6167</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>6618224</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>6582700</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>6655061</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>94,96%</t>
-        </is>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>94,45%</t>
-        </is>
-      </c>
-      <c r="W26" s="2" t="inlineStr">
-        <is>
-          <t>95,49%</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicamentos para el corazón en las dos últimas semanas en 2016</t>
+          <t>Población que ha consumido medicamentos para el corazón en las dos últimas semanas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6691,97 +6691,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>1001</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2044</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>4339</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,25%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0,49%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>1,1%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>1001</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>5002</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,25%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>6028</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,12%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>1,26%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>1001</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>5007</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,12%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,74%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>417419</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>419463</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6839,7 +6839,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>390753</t>
+          <t>391416</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -6854,7 +6854,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -6874,7 +6874,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>810211</t>
+          <t>809190</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -6889,7 +6889,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -7039,7 +7039,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>9405</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7054,7 +7054,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1968</t>
+          <t>1976</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12458</t>
+          <t>11754</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7089,7 +7089,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3784</t>
+          <t>3884</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>16347</t>
+          <t>16310</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,41%</t>
         </is>
       </c>
     </row>
@@ -7147,7 +7147,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>581913</t>
+          <t>581091</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -7162,7 +7162,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>551086</t>
+          <t>551790</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>561576</t>
+          <t>561568</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,7 +7197,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1137693</t>
+          <t>1137730</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1150256</t>
+          <t>1150156</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,66%</t>
         </is>
       </c>
     </row>
@@ -7382,7 +7382,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6766</t>
+          <t>6678</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7397,7 +7397,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1953</t>
+          <t>1932</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11353</t>
+          <t>11479</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3767</t>
+          <t>3717</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15110</t>
+          <t>14284</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7467,7 +7467,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,07%</t>
         </is>
       </c>
     </row>
@@ -7490,7 +7490,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>662331</t>
+          <t>662419</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -7505,7 +7505,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>650033</t>
+          <t>649907</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>659433</t>
+          <t>659454</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,71%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1315373</t>
+          <t>1316199</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1326716</t>
+          <t>1326766</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,7 +7575,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11605</t>
+          <t>11735</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>30027</t>
+          <t>30021</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,82 +7735,82 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
+          <t>1,82%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>4,65%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>14658</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>8345</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>23733</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>2,26%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>1,29%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>3,66%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>34202</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>23369</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>47818</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>2,64%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
           <t>1,8%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>4,65%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>14658</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>8313</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>24238</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>2,26%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>1,28%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>3,73%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>34202</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>23436</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>47924</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>2,64%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>1,81%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,69%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>616021</t>
+          <t>616027</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>634443</t>
+          <t>634313</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7853,77 +7853,77 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
+          <t>98,18%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>588</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>634419</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>625344</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>640732</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>97,74%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>96,34%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>98,71%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>1152</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>1260923</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>1247307</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>1271756</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>97,36%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>96,31%</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
           <t>98,2%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>588</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>634419</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>624839</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>640764</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>97,74%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>96,27%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>98,72%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>1152</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>1260923</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>1247201</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>1271689</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>97,36%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>96,3%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>98,19%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>37435</t>
+          <t>37880</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>66205</t>
+          <t>67648</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7634</t>
+          <t>7750</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>23470</t>
+          <t>23551</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>49533</t>
+          <t>48968</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>83399</t>
+          <t>82548</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,47%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>411713</t>
+          <t>410270</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>440483</t>
+          <t>440038</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>86,15%</t>
+          <t>85,85%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,17%</t>
+          <t>92,07%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>473379</t>
+          <t>473298</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>489215</t>
+          <t>489099</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>891368</t>
+          <t>892219</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>925234</t>
+          <t>925799</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,44%</t>
+          <t>91,53%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>94,98%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>51835</t>
+          <t>54012</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>81971</t>
+          <t>82451</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>24,66%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>39478</t>
+          <t>38002</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>67549</t>
+          <t>65557</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>98393</t>
+          <t>98469</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>138140</t>
+          <t>139801</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>19,63%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>252359</t>
+          <t>251879</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>282495</t>
+          <t>280318</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>75,48%</t>
+          <t>75,34%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>84,5%</t>
+          <t>83,84%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>310213</t>
+          <t>312205</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>338284</t>
+          <t>339760</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>82,12%</t>
+          <t>82,65%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>89,55%</t>
+          <t>89,94%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>573952</t>
+          <t>572291</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>613699</t>
+          <t>613623</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>80,6%</t>
+          <t>80,37%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>86,18%</t>
+          <t>86,17%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>49307</t>
+          <t>49475</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>73941</t>
+          <t>74718</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>28,77%</t>
+          <t>29,07%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>80980</t>
+          <t>79211</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>118467</t>
+          <t>118595</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>29,6%</t>
+          <t>29,64%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>137680</t>
+          <t>136605</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>185675</t>
+          <t>183442</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>27,91%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>183057</t>
+          <t>182280</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>207691</t>
+          <t>207523</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>71,23%</t>
+          <t>70,93%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>80,81%</t>
+          <t>80,75%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>281702</t>
+          <t>281574</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>319189</t>
+          <t>320958</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>70,4%</t>
+          <t>70,36%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>79,76%</t>
+          <t>80,21%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>471492</t>
+          <t>473725</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>519487</t>
+          <t>520562</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>71,75%</t>
+          <t>72,09%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>79,05%</t>
+          <t>79,21%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>173541</t>
+          <t>174520</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>230261</t>
+          <t>230470</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>163842</t>
+          <t>163587</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>219186</t>
+          <t>222624</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9147,7 +9147,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>353330</t>
+          <t>357015</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>434981</t>
+          <t>434160</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,26%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3164089</t>
+          <t>3163880</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3220809</t>
+          <t>3219830</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>93,22%</t>
+          <t>93,21%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>94,86%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3325356</t>
+          <t>3321918</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3380700</t>
+          <t>3380955</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,7 +9255,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>93,72%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6503911</t>
+          <t>6504732</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6585562</t>
+          <t>6581877</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>93,73%</t>
+          <t>93,74%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>94,85%</t>
         </is>
       </c>
     </row>
@@ -9475,7 +9475,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicamentos para el corazón en las dos últimas semanas en 2023</t>
+          <t>Población que ha consumido medicamentos para el corazón en las dos últimas semanas en 2023 (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9670,97 +9670,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>2677</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4435</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>13620</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,85%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>1,11%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>4,35%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>2677</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>14369</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,85%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>13197</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,38%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>4,59%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>2677</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>13749</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,38%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,85%</t>
         </is>
       </c>
     </row>
@@ -9783,12 +9783,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>395552</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9798,12 +9798,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9818,7 +9818,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>298831</t>
+          <t>299580</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -9833,7 +9833,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,65%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -9853,7 +9853,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>699438</t>
+          <t>699990</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -9868,7 +9868,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -10013,97 +10013,97 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>2484</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>2683</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>9680</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>0,49%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>0,63%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>1,89%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>2484</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>8881</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,49%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>8392</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>1,74%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>2484</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>8861</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,9%</t>
         </is>
       </c>
     </row>
@@ -10126,12 +10126,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>420864</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10161,7 +10161,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>502623</t>
+          <t>501824</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -10176,7 +10176,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -10196,7 +10196,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>926190</t>
+          <t>926659</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -10211,7 +10211,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -10356,12 +10356,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1039</t>
+          <t>1033</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10729</t>
+          <t>10876</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10376,7 +10376,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1462</t>
+          <t>1453</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8147</t>
+          <t>8190</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10411,7 +10411,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10426,12 +10426,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3294</t>
+          <t>3203</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>14227</t>
+          <t>14491</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10441,12 +10441,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,34%</t>
         </is>
       </c>
     </row>
@@ -10469,12 +10469,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>525609</t>
+          <t>525462</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>535299</t>
+          <t>535305</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10484,7 +10484,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>534321</t>
+          <t>534278</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>541006</t>
+          <t>541015</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10519,7 +10519,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -10539,12 +10539,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1064579</t>
+          <t>1064315</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1075512</t>
+          <t>1075603</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10554,12 +10554,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,7%</t>
         </is>
       </c>
     </row>
@@ -10699,12 +10699,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10437</t>
+          <t>10934</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>41585</t>
+          <t>42456</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10734,12 +10734,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6238</t>
+          <t>5991</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16382</t>
+          <t>16073</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10749,12 +10749,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10769,12 +10769,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>20322</t>
+          <t>20627</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>49930</t>
+          <t>51951</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10784,12 +10784,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,25%</t>
         </is>
       </c>
     </row>
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>846201</t>
+          <t>845330</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>877349</t>
+          <t>876852</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10827,12 +10827,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,22%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10847,12 +10847,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>696499</t>
+          <t>696808</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>706643</t>
+          <t>706890</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10862,12 +10862,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10882,12 +10882,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1550737</t>
+          <t>1548716</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1580345</t>
+          <t>1580040</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10897,12 +10897,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,71%</t>
         </is>
       </c>
     </row>
@@ -11042,12 +11042,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>30952</t>
+          <t>30941</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>54520</t>
+          <t>55088</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11062,7 +11062,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>17504</t>
+          <t>17860</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>31921</t>
+          <t>32495</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11112,12 +11112,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>52539</t>
+          <t>53330</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>80209</t>
+          <t>80867</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11127,12 +11127,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,32%</t>
         </is>
       </c>
     </row>
@@ -11155,12 +11155,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>505717</t>
+          <t>505149</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>529285</t>
+          <t>529296</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11170,7 +11170,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,27%</t>
+          <t>90,17%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -11190,12 +11190,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>512355</t>
+          <t>511781</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>526772</t>
+          <t>526416</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11205,12 +11205,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>94,03%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11225,12 +11225,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1024304</t>
+          <t>1023646</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1051974</t>
+          <t>1051183</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11240,12 +11240,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,74%</t>
+          <t>92,68%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>95,17%</t>
         </is>
       </c>
     </row>
@@ -11385,12 +11385,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>38501</t>
+          <t>38523</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>58115</t>
+          <t>58395</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11405,7 +11405,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11420,12 +11420,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>13120</t>
+          <t>13738</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>52232</t>
+          <t>53583</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11435,12 +11435,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11455,12 +11455,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>42940</t>
+          <t>41263</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>106137</t>
+          <t>107870</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11470,12 +11470,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>11,05%</t>
         </is>
       </c>
     </row>
@@ -11498,12 +11498,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>310050</t>
+          <t>309770</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>329664</t>
+          <t>329642</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11513,7 +11513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>84,21%</t>
+          <t>84,14%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>556136</t>
+          <t>554785</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>595248</t>
+          <t>594630</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11548,12 +11548,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>91,41%</t>
+          <t>91,19%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11568,12 +11568,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>870396</t>
+          <t>868663</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>933593</t>
+          <t>935270</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11583,12 +11583,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>89,13%</t>
+          <t>88,95%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>95,77%</t>
         </is>
       </c>
     </row>
@@ -11728,12 +11728,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>56561</t>
+          <t>56612</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>78945</t>
+          <t>80834</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>27,92%</t>
+          <t>28,59%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>91345</t>
+          <t>91336</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>116244</t>
+          <t>116150</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>21,5%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>27,37%</t>
+          <t>27,35%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11798,12 +11798,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>154524</t>
+          <t>153438</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>187056</t>
+          <t>188095</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11813,12 +11813,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>26,59%</t>
         </is>
       </c>
     </row>
@@ -11841,12 +11841,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>203814</t>
+          <t>201925</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>226198</t>
+          <t>226147</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11856,12 +11856,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>72,08%</t>
+          <t>71,41%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>80,0%</t>
+          <t>79,98%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11876,12 +11876,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>308481</t>
+          <t>308575</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>333380</t>
+          <t>333389</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11891,12 +11891,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>72,63%</t>
+          <t>72,65%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>78,49%</t>
+          <t>78,5%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11911,12 +11911,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>520428</t>
+          <t>519389</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>552960</t>
+          <t>554046</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11926,12 +11926,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>73,56%</t>
+          <t>73,41%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>78,16%</t>
+          <t>78,31%</t>
         </is>
       </c>
     </row>
@@ -12071,12 +12071,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>141855</t>
+          <t>135483</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>213766</t>
+          <t>213993</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12086,12 +12086,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>144087</t>
+          <t>146292</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>202394</t>
+          <t>203907</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>317171</t>
+          <t>320204</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>406526</t>
+          <t>408796</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12156,12 +12156,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,74%</t>
         </is>
       </c>
     </row>
@@ -12184,12 +12184,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3245054</t>
+          <t>3244827</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3316965</t>
+          <t>3323337</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3455027</t>
+          <t>3453514</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3513334</t>
+          <t>3511129</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>94,42%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>96,0%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12254,12 +12254,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6709715</t>
+          <t>6707445</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6799070</t>
+          <t>6796037</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12269,12 +12269,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>94,29%</t>
+          <t>94,26%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,5%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P16A10-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P16A10-Edad-trans_orig.xlsx
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4164</t>
+          <t>4123</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4459</t>
+          <t>4736</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6422</t>
+          <t>6057</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,63%</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>489900</t>
+          <t>489941</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>463030</t>
+          <t>462753</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>955131</t>
+          <t>955496</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4229</t>
+          <t>4782</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6039</t>
+          <t>6463</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>869</t>
+          <t>873</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8255</t>
+          <t>7509</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,55%</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>731260</t>
+          <t>730707</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>619455</t>
+          <t>619031</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>98,97%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1352727</t>
+          <t>1353473</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1360113</t>
+          <t>1360109</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1814</t>
+          <t>1780</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11015</t>
+          <t>10109</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3371</t>
+          <t>3113</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16202</t>
+          <t>14567</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6410</t>
+          <t>6858</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>21182</t>
+          <t>20421</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,54%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>626634</t>
+          <t>627540</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>635835</t>
+          <t>635869</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>673542</t>
+          <t>675177</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>686373</t>
+          <t>686631</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,55%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1306212</t>
+          <t>1306973</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1320984</t>
+          <t>1320536</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,48%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7352</t>
+          <t>6279</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>22980</t>
+          <t>22836</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10295</t>
+          <t>10286</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>26581</t>
+          <t>27430</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>20926</t>
+          <t>20058</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>42851</t>
+          <t>43271</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,18%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>496167</t>
+          <t>496311</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>511795</t>
+          <t>512868</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>95,6%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>489061</t>
+          <t>488212</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>505347</t>
+          <t>505356</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>94,68%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>991938</t>
+          <t>991518</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1013863</t>
+          <t>1014731</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>95,82%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>98,06%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>32053</t>
+          <t>32292</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>57520</t>
+          <t>56448</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>16451</t>
+          <t>15603</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>35655</t>
+          <t>35060</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>54659</t>
+          <t>52756</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>85699</t>
+          <t>83645</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,58%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>329190</t>
+          <t>330262</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>354657</t>
+          <t>354418</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>85,13%</t>
+          <t>85,4%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>91,71%</t>
+          <t>91,65%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>368331</t>
+          <t>368926</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>387535</t>
+          <t>388383</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,17%</t>
+          <t>91,32%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>704997</t>
+          <t>707051</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>736037</t>
+          <t>737940</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,16%</t>
+          <t>89,42%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,09%</t>
+          <t>93,33%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>39910</t>
+          <t>40086</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>64559</t>
+          <t>63942</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>39922</t>
+          <t>40416</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>65988</t>
+          <t>65485</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>85907</t>
+          <t>85090</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>120939</t>
+          <t>120257</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>18,92%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>228024</t>
+          <t>228641</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>252673</t>
+          <t>252497</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>77,93%</t>
+          <t>78,15%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>86,36%</t>
+          <t>86,3%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>276946</t>
+          <t>277449</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>303012</t>
+          <t>302518</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>80,76%</t>
+          <t>80,9%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>88,36%</t>
+          <t>88,21%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>514578</t>
+          <t>515260</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>549610</t>
+          <t>550427</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>80,97%</t>
+          <t>81,08%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>86,48%</t>
+          <t>86,61%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>50464</t>
+          <t>53081</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>77723</t>
+          <t>78544</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>25,29%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>37,03%</t>
+          <t>37,42%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>59415</t>
+          <t>59312</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>91705</t>
+          <t>91889</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>27,52%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>121059</t>
+          <t>119387</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>159335</t>
+          <t>161323</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>29,3%</t>
+          <t>29,67%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>132160</t>
+          <t>131339</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>159419</t>
+          <t>156802</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>62,97%</t>
+          <t>62,58%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>75,96%</t>
+          <t>74,71%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>242203</t>
+          <t>242019</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>274493</t>
+          <t>274596</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>72,54%</t>
+          <t>72,48%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>82,21%</t>
+          <t>82,24%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>384456</t>
+          <t>382468</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>422732</t>
+          <t>424404</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>70,7%</t>
+          <t>70,33%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>77,74%</t>
+          <t>78,05%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>153538</t>
+          <t>153862</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>202598</t>
+          <t>202443</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>154493</t>
+          <t>155486</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>207824</t>
+          <t>205837</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>322063</t>
+          <t>319303</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>393925</t>
+          <t>393067</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,91%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3072927</t>
+          <t>3073082</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3121987</t>
+          <t>3121663</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>93,82%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>95,3%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3171373</t>
+          <t>3173360</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3224704</t>
+          <t>3223711</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>93,91%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>95,4%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6260797</t>
+          <t>6261655</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6332659</t>
+          <t>6335419</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>94,09%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>95,2%</t>
         </is>
       </c>
     </row>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4829</t>
+          <t>4347</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3732,7 +3732,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5660</t>
+          <t>5982</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3767,7 +3767,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3787,7 +3787,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6833</t>
+          <t>6911</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3802,7 +3802,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,78%</t>
         </is>
       </c>
     </row>
@@ -3825,7 +3825,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>448276</t>
+          <t>448758</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>423679</t>
+          <t>423357</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -3875,7 +3875,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -3895,7 +3895,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>875612</t>
+          <t>875534</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1030</t>
+          <t>1031</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11374</t>
+          <t>11053</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4075,7 +4075,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4095,7 +4095,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4344</t>
+          <t>3948</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4110,7 +4110,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1870</t>
+          <t>1033</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13573</t>
+          <t>11586</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>0,89%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>674864</t>
+          <t>675185</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>685208</t>
+          <t>685207</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,7 +4183,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -4203,7 +4203,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>604870</t>
+          <t>605266</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -4218,7 +4218,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1281878</t>
+          <t>1283865</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1293581</t>
+          <t>1294418</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,86%</t>
+          <t>99,92%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1927</t>
+          <t>1853</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11078</t>
+          <t>10981</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4939</t>
+          <t>4717</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18959</t>
+          <t>18312</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8893</t>
+          <t>8126</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>25694</t>
+          <t>24191</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,74%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>668976</t>
+          <t>669073</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>678127</t>
+          <t>678201</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>99,73%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>689873</t>
+          <t>690520</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>703893</t>
+          <t>704115</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1363192</t>
+          <t>1364695</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1379993</t>
+          <t>1380760</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,41%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6611</t>
+          <t>7473</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>23018</t>
+          <t>23920</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3230</t>
+          <t>3219</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15161</t>
+          <t>15086</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>13499</t>
+          <t>12862</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>33311</t>
+          <t>32438</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,64%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>591599</t>
+          <t>590697</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>608006</t>
+          <t>607144</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>598911</t>
+          <t>598986</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>610842</t>
+          <t>610853</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1195378</t>
+          <t>1196251</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1215190</t>
+          <t>1215827</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,95%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>26395</t>
+          <t>25761</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>47464</t>
+          <t>49057</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>18351</t>
+          <t>18418</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>37433</t>
+          <t>37645</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>48209</t>
+          <t>48222</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>79476</t>
+          <t>77906</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5174,7 +5174,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>8,9%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>380880</t>
+          <t>379287</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>401949</t>
+          <t>402583</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>88,92%</t>
+          <t>88,55%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,84%</t>
+          <t>93,99%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>409343</t>
+          <t>409131</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>428425</t>
+          <t>428358</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,62%</t>
+          <t>91,57%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>95,88%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>795643</t>
+          <t>797213</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>826910</t>
+          <t>826897</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,7 +5282,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,92%</t>
+          <t>91,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>35322</t>
+          <t>35056</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>61236</t>
+          <t>59508</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>27108</t>
+          <t>27301</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>50540</t>
+          <t>50363</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>68688</t>
+          <t>68718</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>102590</t>
+          <t>102290</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>15,48%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>246559</t>
+          <t>248287</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>272473</t>
+          <t>272739</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>80,11%</t>
+          <t>80,67%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>88,52%</t>
+          <t>88,61%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>302461</t>
+          <t>302638</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>325893</t>
+          <t>325700</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>85,68%</t>
+          <t>85,73%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,32%</t>
+          <t>92,27%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>558206</t>
+          <t>558506</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>592108</t>
+          <t>592078</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>84,47%</t>
+          <t>84,52%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>89,61%</t>
+          <t>89,6%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>59491</t>
+          <t>59895</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>91696</t>
+          <t>90414</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>23,97%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>36,7%</t>
+          <t>36,19%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>71001</t>
+          <t>70803</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>104574</t>
+          <t>105740</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>18,25%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>26,96%</t>
+          <t>27,26%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>139697</t>
+          <t>140529</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>184936</t>
+          <t>185864</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>22,03%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>29,0%</t>
+          <t>29,14%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>158155</t>
+          <t>159437</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>190360</t>
+          <t>189956</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>63,3%</t>
+          <t>63,81%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>76,19%</t>
+          <t>76,03%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>283362</t>
+          <t>282196</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>316935</t>
+          <t>317133</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>73,04%</t>
+          <t>72,74%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>81,7%</t>
+          <t>81,75%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>452851</t>
+          <t>451923</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>498090</t>
+          <t>497258</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>71,0%</t>
+          <t>70,86%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>78,1%</t>
+          <t>77,97%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>155255</t>
+          <t>154266</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>211198</t>
+          <t>214229</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>146419</t>
+          <t>145695</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>199323</t>
+          <t>196463</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>312413</t>
+          <t>314378</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>388024</t>
+          <t>386052</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,54%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3208805</t>
+          <t>3205774</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3264748</t>
+          <t>3265737</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>93,74%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,49%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3349847</t>
+          <t>3352707</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3402751</t>
+          <t>3403475</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>94,46%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6581149</t>
+          <t>6583121</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6656760</t>
+          <t>6654795</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>94,46%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,49%</t>
         </is>
       </c>
     </row>
@@ -6731,7 +6731,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4339</t>
+          <t>4351</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6766,7 +6766,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6028</t>
+          <t>5608</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6781,7 +6781,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,69%</t>
         </is>
       </c>
     </row>
@@ -6839,7 +6839,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>391416</t>
+          <t>391404</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -6874,7 +6874,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>809190</t>
+          <t>809610</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -6889,7 +6889,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -7039,7 +7039,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9405</t>
+          <t>10186</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7054,7 +7054,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1976</t>
+          <t>1952</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11754</t>
+          <t>12105</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7089,7 +7089,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3884</t>
+          <t>3791</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>16310</t>
+          <t>15376</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,33%</t>
         </is>
       </c>
     </row>
@@ -7147,7 +7147,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>581091</t>
+          <t>580310</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -7162,7 +7162,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>551790</t>
+          <t>551439</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>561568</t>
+          <t>561592</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,7 +7197,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1137730</t>
+          <t>1138664</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1150156</t>
+          <t>1150249</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,67%</t>
         </is>
       </c>
     </row>
@@ -7382,7 +7382,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6678</t>
+          <t>6408</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7397,7 +7397,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1932</t>
+          <t>2796</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11479</t>
+          <t>11450</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3717</t>
+          <t>3729</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>14284</t>
+          <t>14643</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7467,7 +7467,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,1%</t>
         </is>
       </c>
     </row>
@@ -7490,7 +7490,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>662419</t>
+          <t>662689</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -7505,7 +7505,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>649907</t>
+          <t>649936</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>659454</t>
+          <t>658590</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,58%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1316199</t>
+          <t>1315840</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1326766</t>
+          <t>1326754</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,7 +7575,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11735</t>
+          <t>11687</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>30021</t>
+          <t>29621</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8345</t>
+          <t>7464</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>23733</t>
+          <t>24247</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>23369</t>
+          <t>24339</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>47818</t>
+          <t>49501</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,82%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>616027</t>
+          <t>616427</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>634313</t>
+          <t>634361</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>625344</t>
+          <t>624830</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>640732</t>
+          <t>641613</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1247307</t>
+          <t>1245624</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1271756</t>
+          <t>1270786</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,12%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>37880</t>
+          <t>38204</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>67648</t>
+          <t>66680</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7750</t>
+          <t>7877</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>23551</t>
+          <t>23549</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,7 +8113,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>48968</t>
+          <t>50746</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>82548</t>
+          <t>83629</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,58%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>410270</t>
+          <t>411238</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>440038</t>
+          <t>439714</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>85,85%</t>
+          <t>86,05%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,07%</t>
+          <t>92,01%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>473298</t>
+          <t>473300</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>489099</t>
+          <t>488972</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8231,7 +8231,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>892219</t>
+          <t>891138</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>925799</t>
+          <t>924021</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>91,42%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>94,79%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>54012</t>
+          <t>51847</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>82451</t>
+          <t>81852</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>24,48%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>38002</t>
+          <t>38271</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>65557</t>
+          <t>64484</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>98469</t>
+          <t>100193</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>139801</t>
+          <t>138920</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>19,51%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>251879</t>
+          <t>252478</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>280318</t>
+          <t>282483</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>75,34%</t>
+          <t>75,52%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>83,84%</t>
+          <t>84,49%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>312205</t>
+          <t>313278</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>339760</t>
+          <t>339491</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>82,65%</t>
+          <t>82,93%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>89,94%</t>
+          <t>89,87%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>572291</t>
+          <t>573172</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>613623</t>
+          <t>611899</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>80,37%</t>
+          <t>80,49%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>86,17%</t>
+          <t>85,93%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>49475</t>
+          <t>49921</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>74718</t>
+          <t>74260</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>19,42%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>28,9%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>79211</t>
+          <t>81299</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>118595</t>
+          <t>118333</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>29,64%</t>
+          <t>29,57%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>136605</t>
+          <t>138276</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>183442</t>
+          <t>181928</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>27,68%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>182280</t>
+          <t>182738</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>207523</t>
+          <t>207077</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>70,93%</t>
+          <t>71,1%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>80,75%</t>
+          <t>80,58%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>281574</t>
+          <t>281836</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>320958</t>
+          <t>318870</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>70,36%</t>
+          <t>70,43%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>80,21%</t>
+          <t>79,68%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>473725</t>
+          <t>475239</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>520562</t>
+          <t>518891</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>72,09%</t>
+          <t>72,32%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>79,21%</t>
+          <t>78,96%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>174520</t>
+          <t>176028</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>230470</t>
+          <t>232086</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>163587</t>
+          <t>163437</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>222624</t>
+          <t>222554</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,7 +9142,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>357015</t>
+          <t>358205</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>434160</t>
+          <t>438331</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,32%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3163880</t>
+          <t>3162264</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3219830</t>
+          <t>3218322</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>93,16%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>94,81%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3321918</t>
+          <t>3321988</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3380955</t>
+          <t>3381105</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,39%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6504732</t>
+          <t>6500561</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6581877</t>
+          <t>6580687</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>93,68%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>94,84%</t>
         </is>
       </c>
     </row>
@@ -9700,7 +9700,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2677</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -9710,7 +9710,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13620</t>
+          <t>15430</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9725,7 +9725,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9735,7 +9735,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>2677</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -9745,12 +9745,12 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13197</t>
+          <t>18893</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -9760,7 +9760,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>2,45%</t>
         </is>
       </c>
     </row>
@@ -9778,7 +9778,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -9813,17 +9813,17 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>310523</t>
+          <t>359431</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>299580</t>
+          <t>347082</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9833,7 +9833,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -9848,27 +9848,27 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>710510</t>
+          <t>767224</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>699990</t>
+          <t>751412</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,6%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>97,55%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -9891,17 +9891,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9926,17 +9926,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9961,17 +9961,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10043,7 +10043,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2484</t>
+          <t>1964</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -10053,12 +10053,12 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9680</t>
+          <t>6333</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -10068,7 +10068,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10078,7 +10078,7 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>2484</t>
+          <t>1964</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
@@ -10088,12 +10088,12 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8392</t>
+          <t>6703</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
@@ -10103,7 +10103,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,69%</t>
         </is>
       </c>
     </row>
@@ -10121,7 +10121,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -10156,27 +10156,27 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>509020</t>
+          <t>499119</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>501824</t>
+          <t>494750</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,61%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -10191,27 +10191,27 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>932567</t>
+          <t>976009</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>926659</t>
+          <t>971270</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>99,8%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -10234,17 +10234,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10269,17 +10269,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10304,17 +10304,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10351,67 +10351,67 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>3762</t>
+          <t>3797</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1033</t>
+          <t>1154</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10876</t>
+          <t>11307</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
+          <t>0,61%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,19%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>1,82%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>4369</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>1486</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>8809</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
           <t>0,7%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,19%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>2,03%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>3785</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>1453</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>8190</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,7%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10421,32 +10421,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>7547</t>
+          <t>8166</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3203</t>
+          <t>3575</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>14491</t>
+          <t>15642</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,26%</t>
         </is>
       </c>
     </row>
@@ -10464,67 +10464,67 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>532576</t>
+          <t>617040</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>525462</t>
+          <t>609530</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>535305</t>
+          <t>619683</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
+          <t>99,39%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>98,18%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>99,81%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>840</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>617770</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>613330</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>620653</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
           <t>99,3%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>97,97%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>99,81%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>840</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>538683</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>534278</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>541015</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>99,3%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>99,76%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10534,32 +10534,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1071259</t>
+          <t>1234810</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1064315</t>
+          <t>1227334</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1075603</t>
+          <t>1239401</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,71%</t>
         </is>
       </c>
     </row>
@@ -10577,17 +10577,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10612,17 +10612,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10647,17 +10647,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1078806</t>
+          <t>1242976</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1078806</t>
+          <t>1242976</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1078806</t>
+          <t>1242976</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10694,32 +10694,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>25858</t>
+          <t>27616</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10934</t>
+          <t>18736</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>42456</t>
+          <t>39467</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10729,32 +10729,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>10470</t>
+          <t>11668</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5991</t>
+          <t>6928</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16073</t>
+          <t>18047</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10764,32 +10764,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>36327</t>
+          <t>39284</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>20627</t>
+          <t>28603</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>51951</t>
+          <t>52142</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,63%</t>
         </is>
       </c>
     </row>
@@ -10807,32 +10807,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>861928</t>
+          <t>673001</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>845330</t>
+          <t>661150</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>876852</t>
+          <t>681881</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10842,32 +10842,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>702411</t>
+          <t>725218</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>696808</t>
+          <t>718839</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>706890</t>
+          <t>729958</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,55%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10877,32 +10877,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1564340</t>
+          <t>1398220</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1548716</t>
+          <t>1385362</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1580040</t>
+          <t>1408901</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,01%</t>
         </is>
       </c>
     </row>
@@ -10920,17 +10920,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10955,17 +10955,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10990,17 +10990,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11037,32 +11037,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>41995</t>
+          <t>46170</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>30941</t>
+          <t>35814</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>55088</t>
+          <t>59443</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11072,22 +11072,22 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>24012</t>
+          <t>27604</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>17860</t>
+          <t>19917</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>32495</t>
+          <t>36675</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -11097,7 +11097,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11107,32 +11107,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>66007</t>
+          <t>73774</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>53330</t>
+          <t>61007</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>80867</t>
+          <t>91799</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,55%</t>
         </is>
       </c>
     </row>
@@ -11150,32 +11150,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>518242</t>
+          <t>562189</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>505149</t>
+          <t>548916</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>529296</t>
+          <t>572545</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>92,5%</t>
+          <t>92,41%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,17%</t>
+          <t>90,23%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,48%</t>
+          <t>94,11%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11185,27 +11185,27 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>520264</t>
+          <t>579132</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>511781</t>
+          <t>570061</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>526416</t>
+          <t>586819</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,45%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>93,96%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -11220,32 +11220,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1038506</t>
+          <t>1141321</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1023646</t>
+          <t>1123296</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1051183</t>
+          <t>1154088</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>94,02%</t>
+          <t>93,93%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,68%</t>
+          <t>92,45%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>94,98%</t>
         </is>
       </c>
     </row>
@@ -11263,17 +11263,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>560237</t>
+          <t>608359</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>560237</t>
+          <t>608359</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>560237</t>
+          <t>608359</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11298,17 +11298,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>544276</t>
+          <t>606736</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>544276</t>
+          <t>606736</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>544276</t>
+          <t>606736</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11333,17 +11333,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1104513</t>
+          <t>1215095</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1104513</t>
+          <t>1215095</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1104513</t>
+          <t>1215095</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11380,32 +11380,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>47604</t>
+          <t>50801</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>38523</t>
+          <t>40629</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>58395</t>
+          <t>61470</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11415,32 +11415,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>32660</t>
+          <t>36381</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>13738</t>
+          <t>28653</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>53583</t>
+          <t>44737</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11450,32 +11450,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>80264</t>
+          <t>87181</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>41263</t>
+          <t>74841</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>107870</t>
+          <t>102307</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>12,09%</t>
         </is>
       </c>
     </row>
@@ -11493,32 +11493,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>320561</t>
+          <t>356279</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>309770</t>
+          <t>345610</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>329642</t>
+          <t>366451</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>87,07%</t>
+          <t>87,52%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>84,14%</t>
+          <t>84,9%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>89,54%</t>
+          <t>90,02%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11528,32 +11528,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>575708</t>
+          <t>402785</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>554785</t>
+          <t>394429</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>594630</t>
+          <t>410513</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>94,63%</t>
+          <t>91,72%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>91,19%</t>
+          <t>89,81%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>93,48%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11563,32 +11563,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>896269</t>
+          <t>759065</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>868663</t>
+          <t>743939</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>935270</t>
+          <t>771405</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>91,78%</t>
+          <t>89,7%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>88,95%</t>
+          <t>87,91%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>91,16%</t>
         </is>
       </c>
     </row>
@@ -11606,17 +11606,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11641,17 +11641,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11676,17 +11676,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11723,32 +11723,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>67334</t>
+          <t>75850</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>56612</t>
+          <t>64181</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>80834</t>
+          <t>89792</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>24,45%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>28,95%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11758,32 +11758,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>103443</t>
+          <t>113779</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>91336</t>
+          <t>99870</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>116150</t>
+          <t>128238</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>24,55%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>21,55%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>27,35%</t>
+          <t>27,67%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11793,32 +11793,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>170777</t>
+          <t>189629</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>153438</t>
+          <t>172566</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>188095</t>
+          <t>208098</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>24,51%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>22,31%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>26,9%</t>
         </is>
       </c>
     </row>
@@ -11836,32 +11836,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>215425</t>
+          <t>234348</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>201925</t>
+          <t>220406</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>226147</t>
+          <t>246017</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>76,19%</t>
+          <t>75,55%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>71,41%</t>
+          <t>71,05%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>79,98%</t>
+          <t>79,31%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11871,32 +11871,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>321282</t>
+          <t>349631</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>308575</t>
+          <t>335172</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>333389</t>
+          <t>363540</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>75,64%</t>
+          <t>75,45%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>72,65%</t>
+          <t>72,33%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>78,5%</t>
+          <t>78,45%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11906,32 +11906,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>536707</t>
+          <t>583979</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>519389</t>
+          <t>565510</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>554046</t>
+          <t>601042</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>75,86%</t>
+          <t>75,49%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>73,41%</t>
+          <t>73,1%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>78,31%</t>
+          <t>77,69%</t>
         </is>
       </c>
     </row>
@@ -11949,17 +11949,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11984,17 +11984,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>424725</t>
+          <t>463410</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>424725</t>
+          <t>463410</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>424725</t>
+          <t>463410</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12019,17 +12019,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>707484</t>
+          <t>773608</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>707484</t>
+          <t>773608</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>707484</t>
+          <t>773608</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12066,32 +12066,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>186554</t>
+          <t>204233</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>135483</t>
+          <t>180299</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>213993</t>
+          <t>230228</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12101,32 +12101,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>179530</t>
+          <t>198846</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>146292</t>
+          <t>179190</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>203907</t>
+          <t>222350</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12136,32 +12136,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>366084</t>
+          <t>403079</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>320204</t>
+          <t>370759</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>408796</t>
+          <t>439152</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>6,05%</t>
         </is>
       </c>
     </row>
@@ -12179,32 +12179,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>3272266</t>
+          <t>3327542</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3244827</t>
+          <t>3301547</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3323337</t>
+          <t>3351476</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>94,22%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>93,48%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>94,89%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12214,32 +12214,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>3477891</t>
+          <t>3533087</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3453514</t>
+          <t>3509583</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3511129</t>
+          <t>3552743</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>94,67%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>94,04%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12249,32 +12249,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>6750157</t>
+          <t>6860628</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6707445</t>
+          <t>6824555</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6796037</t>
+          <t>6892948</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>94,45%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>93,95%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>94,9%</t>
         </is>
       </c>
     </row>
@@ -12292,17 +12292,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3458820</t>
+          <t>3531775</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3458820</t>
+          <t>3531775</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3458820</t>
+          <t>3531775</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12327,17 +12327,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3657421</t>
+          <t>3731933</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3657421</t>
+          <t>3731933</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3657421</t>
+          <t>3731933</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12362,17 +12362,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7116241</t>
+          <t>7263707</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7116241</t>
+          <t>7263707</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7116241</t>
+          <t>7263707</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
